--- a/outputs/daily/predictions_2026-06-18.xlsx
+++ b/outputs/daily/predictions_2026-06-18.xlsx
@@ -843,31 +843,31 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.405057058126711</v>
+        <v>1.39225926531888</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9451992825455231</v>
+        <v>0.9414970753533547</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5255730332283852</v>
+        <v>0.5232611773510661</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2687379643627598</v>
+        <v>0.2693884479852093</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2056890024088549</v>
+        <v>0.2073503746637245</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.447748365711666</v>
+        <v>0.4417787281583138</v>
       </c>
       <c r="R2" t="n">
-        <v>1.586155800829463</v>
+        <v>1.562887086633405</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8838441991705377</v>
+        <v>0.877112913366595</v>
       </c>
       <c r="T2" t="n">
         <v>0.4796870447989138</v>
@@ -885,58 +885,58 @@
         <v>0.4873714082952134</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4634381407470156</v>
+        <v>0.460827211794766</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2960806765316035</v>
+        <v>0.2976257033012168</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2404811827213807</v>
+        <v>0.241547084904017</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4172425363592639</v>
+        <v>0.4128923625035615</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5827574636407361</v>
+        <v>0.5871076374964386</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4740518386913118</v>
+        <v>0.4710800193289505</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5259481613086882</v>
+        <v>0.5289199806710495</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.463075</v>
+        <v>0.459845</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.29559</v>
+        <v>0.297985</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.241335</v>
+        <v>0.24217</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.41718</v>
+        <v>0.41274</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.473465</v>
+        <v>0.470625</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.40486</v>
+        <v>1.392125</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.946165</v>
+        <v>0.94278</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.351025</v>
+        <v>2.334905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.4939792141577279</v>
+        <v>0.4924017395687378</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2708043794211228</v>
+        <v>0.2714508295625059</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2352164064211494</v>
+        <v>0.2361474308687563</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.4939792141577279</v>
+        <v>0.4924017395687378</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,16 +955,16 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>4.861708639202142</v>
+        <v>4.822754729147579</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2352164064211494</v>
+        <v>0.2361474308687563</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.02952740401229453</v>
+        <v>0.02879705620503176</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1435536351797844</v>
+        <v>0.1388811389983455</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -972,16 +972,16 @@
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1.810768747273446</v>
+        <v>1.791404323774326</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.5827574636407361</v>
+        <v>0.5871076374964386</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.03050582935240209</v>
+        <v>0.02888636565475233</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.05523900240098678</v>
+        <v>0.05174716033204962</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.1392857859909509</v>
+        <v>0.1397637018540726</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.1213024653022965</v>
+        <v>0.122247268366268</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="BI2" t="n">
-        <v>0.1080070910070784</v>
+        <v>0.1096367742684797</v>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0.09411410055254986</v>
+        <v>0.09394482369695732</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>0.08895658031968734</v>
+        <v>0.08844877675527187</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>0.07745744211350254</v>
+        <v>0.07855444610765501</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.0598421931761073</v>
+        <v>0.059812325698258</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="BS2" t="n">
-        <v>0.04407856041686906</v>
+        <v>0.0435985170736125</v>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
@@ -1053,7 +1053,7 @@
         </is>
       </c>
       <c r="BU2" t="n">
-        <v>0.04259057867435771</v>
+        <v>0.04296062320300575</v>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.04204084794793583</v>
+        <v>0.04163713231683511</v>
       </c>
     </row>
     <row r="3">
@@ -1114,31 +1114,31 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.827858408534345</v>
+        <v>1.82743379709738</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8206887296653447</v>
+        <v>0.8266133411023098</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6155802865674639</v>
+        <v>0.6123033288568352</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2332400162129562</v>
+        <v>0.2330124140215624</v>
       </c>
       <c r="P3" t="n">
-        <v>0.15117969721958</v>
+        <v>0.1546842571216024</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4893891533750043</v>
+        <v>0.4922776445709156</v>
       </c>
       <c r="R3" t="n">
-        <v>1.832693166229903</v>
+        <v>1.831921145435421</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7973068337700973</v>
+        <v>0.8080788545645793</v>
       </c>
       <c r="T3" t="n">
         <v>0.7267653147951589</v>
@@ -1156,58 +1156,58 @@
         <v>0.4468053648956409</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.6017238422989507</v>
+        <v>0.6001102709606068</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2452206759706428</v>
+        <v>0.2454734932030115</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1530554817304065</v>
+        <v>0.1544162358363816</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4936866920509528</v>
+        <v>0.4950506735152501</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5063133079490472</v>
+        <v>0.50494932648475</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4804815678902851</v>
+        <v>0.4826406112493169</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5195184321097149</v>
+        <v>0.5173593887506831</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.60275</v>
+        <v>0.601085</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.242935</v>
+        <v>0.243105</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.154315</v>
+        <v>0.15581</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.49417</v>
+        <v>0.49557</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.479375</v>
+        <v>0.481455</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.828265</v>
+        <v>1.827805</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.821615</v>
+        <v>0.82774</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.64988</v>
+        <v>2.655545</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6510309353800289</v>
+        <v>0.6493167594611914</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2124084501064563</v>
+        <v>0.2123806135379909</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1365606145135149</v>
+        <v>0.1383026270008177</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.6510309353800289</v>
+        <v>0.6493167594611914</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>1.624483470021592</v>
+        <v>1.633177467558425</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.6510309353800289</v>
+        <v>0.6493167594611914</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.03545064881256499</v>
+        <v>0.03701343060435613</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.05758899299755238</v>
+        <v>0.06044950086007184</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1.624483470021592</v>
+        <v>1.633177467558425</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.6510309353800289</v>
+        <v>0.6493167594611914</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.03545064881256499</v>
+        <v>0.03701343060435613</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.05758899299755238</v>
+        <v>0.06044950086007184</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1187147843155296</v>
+        <v>0.1179600339576216</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1181972210865941</v>
+        <v>0.1174943130473121</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1167524130399611</v>
+        <v>0.1169230901881173</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.0970031272235308</v>
+        <v>0.09712236666855933</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.08136804513780629</v>
+        <v>0.08099548085501972</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.07201592814284134</v>
+        <v>0.07157102620979922</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.0591026605832192</v>
+        <v>0.05916156510140312</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.04745331009194499</v>
+        <v>0.04753619264189024</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04355335888324057</v>
+        <v>0.04393190283291195</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03980468662732264</v>
+        <v>0.04014132200383071</v>
       </c>
     </row>
     <row r="4">
@@ -1385,31 +1385,31 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>1.990235529859082</v>
+        <v>1.992824846575189</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7143317878382718</v>
+        <v>0.7172424711221645</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7404949716465126</v>
+        <v>0.7396218707264559</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1726437187594802</v>
+        <v>0.1722209212757305</v>
       </c>
       <c r="P4" t="n">
-        <v>0.08686130959400722</v>
+        <v>0.08815720799781364</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5550222576973074</v>
+        <v>0.5564110947721029</v>
       </c>
       <c r="R4" t="n">
-        <v>2.194600289443376</v>
+        <v>2.199308138018117</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7053997105566236</v>
+        <v>0.7106918619818832</v>
       </c>
       <c r="T4" t="n">
         <v>0.5483809775437125</v>
@@ -1427,58 +1427,58 @@
         <v>0.3836362297162483</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6644223055513554</v>
+        <v>0.6642092875643173</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2206795282358758</v>
+        <v>0.2205399025805051</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1148981662127689</v>
+        <v>0.1152508098551776</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5074897626177084</v>
+        <v>0.5088344651343412</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4925102373822916</v>
+        <v>0.4911655348656588</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4502274378959189</v>
+        <v>0.4516353973037406</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5497725621040811</v>
+        <v>0.5483646026962594</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.666525</v>
+        <v>0.66628</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.218915</v>
+        <v>0.2189</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.11456</v>
+        <v>0.11482</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.507155</v>
+        <v>0.50843</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.44946</v>
+        <v>0.451025</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.991665</v>
+        <v>1.9943</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.712465</v>
+        <v>0.71512</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.70413</v>
+        <v>2.70942</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6542369071867432</v>
+        <v>0.653834412321961</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2475638256374877</v>
+        <v>0.2473598002301451</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.09819926717576907</v>
+        <v>0.09880578744789381</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.6542369071867432</v>
+        <v>0.653834412321961</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
@@ -1497,16 +1497,16 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>5.792275601947365</v>
+        <v>5.806495474489839</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2475638256374877</v>
+        <v>0.2473598002301451</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.07492010687800751</v>
+        <v>0.07513887895441465</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.4339579071647719</v>
+        <v>0.4362935606070486</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>5.792275601947365</v>
+        <v>5.806495474489839</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.2475638256374877</v>
+        <v>0.2473598002301451</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.07492010687800751</v>
+        <v>0.07513887895441465</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4339579071647719</v>
+        <v>0.4362935606070486</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1324962973482056</v>
+        <v>0.1321126708198408</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>0.1236352821620538</v>
+        <v>0.1230785426848365</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>0.1046217365748023</v>
+        <v>0.1046077888009474</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>0.09464631696669498</v>
+        <v>0.09475681848537169</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>0.08789961285239081</v>
+        <v>0.08775913765239589</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>0.07641086204882802</v>
+        <v>0.07604266156368276</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>0.06278948759914027</v>
+        <v>0.06294458075335461</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="BS4" t="n">
-        <v>0.04373523313992155</v>
+        <v>0.04372214750692669</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.03827758326950965</v>
+        <v>0.03821039578708188</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.03397028733373784</v>
+        <v>0.03410415860828044</v>
       </c>
     </row>
     <row r="5">
